--- a/Compititor's_Price/Cladco_Prices/Cladco_Prices_14-11-2025.xlsx
+++ b/Compititor's_Price/Cladco_Prices/Cladco_Prices_14-11-2025.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -483,7 +483,30 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-hollow-grooved-composite-decking-board-in-charcoal</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -530,7 +553,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Error: 404 Client Error: Not Found for url: https://www.roofingoutlet.co.uk/products/cladco-hollow-domestic-grade-composite-decking-board-4m?variant=40028699099207</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.roofingoutlet.co.uk/products/cladco-hollow-domestic-grade-composite-decking-board-4m?variant=40028699099207</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -589,12 +612,35 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>£20.80</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/cladco-composite-decking-board-hollow-150mm-x-25mm-x-4m-all-colours?variant=41749782429889</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/22-hollow-domestic-grade</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -663,7 +709,7 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>£20.80</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://build4less.co.uk/products/cladco-composite-decking-board-hollow-150mm-x-25mm-x-4m-all-colours?variant=41749782495425</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -779,7 +825,30 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -816,7 +885,30 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -853,7 +945,30 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -890,7 +1005,30 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -927,7 +1065,30 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -964,7 +1125,30 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1001,7 +1185,30 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -1038,7 +1245,30 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-woodgrain-effect-hollow-domestic-grade-composite-decking-boards</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -1075,7 +1305,30 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -1112,7 +1365,30 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -1149,7 +1425,30 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -1159,7 +1458,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>£10.92</t>
+          <t>Error: 503 Server Error: Service Unavailable for url: https://www.roofingoutlet.co.uk/products/cladco-woodgrain-effect-hollow-composite-decking-board-2-4m-all-colours?variant=40043049680967</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1186,7 +1485,30 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -1223,7 +1545,30 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -1260,7 +1605,30 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -1297,7 +1665,30 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
@@ -1334,7 +1725,30 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4-composite-woodgrain-decking</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
@@ -1371,7 +1785,30 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
@@ -1408,7 +1845,30 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
@@ -1445,7 +1905,30 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
@@ -1482,7 +1965,30 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
@@ -1519,7 +2025,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
@@ -1556,7 +2085,30 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
@@ -1593,7 +2145,30 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
@@ -1630,7 +2205,30 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-commercial-grade-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -1704,7 +2302,30 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -1815,7 +2436,30 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
@@ -1852,7 +2496,30 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/4m-solid-bullnose-composite-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
@@ -2000,7 +2667,30 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
@@ -2037,7 +2727,30 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
@@ -2074,7 +2787,30 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
@@ -2111,7 +2847,30 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
@@ -2148,7 +2907,30 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
@@ -2185,7 +2967,30 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
@@ -2222,7 +3027,30 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
@@ -2259,7 +3087,30 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2-4m-composite-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
@@ -2296,7 +3147,30 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
@@ -2333,7 +3207,30 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -2370,7 +3267,30 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E53" t="inlineStr">
@@ -2407,7 +3327,30 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -2444,7 +3387,30 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E55" t="inlineStr">
@@ -2481,7 +3447,30 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E56" t="inlineStr">
@@ -2518,7 +3507,30 @@
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -2555,7 +3567,30 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-corner-trim-60x50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E58" t="inlineStr">
@@ -2592,7 +3627,30 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E59" t="inlineStr">
@@ -2629,7 +3687,30 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
@@ -2666,7 +3747,30 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E61" t="inlineStr">
@@ -2703,7 +3807,30 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E62" t="inlineStr">
@@ -2740,7 +3867,30 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E63" t="inlineStr">
@@ -2777,7 +3927,30 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E64" t="inlineStr">
@@ -2814,7 +3987,30 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E65" t="inlineStr">
@@ -2851,7 +4047,30 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">
@@ -2888,7 +4107,30 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E67" t="inlineStr">
@@ -2925,7 +4167,30 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-skirting-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E68" t="inlineStr">
@@ -2962,7 +4227,30 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E69" t="inlineStr">
@@ -2999,7 +4287,30 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
@@ -3036,7 +4347,30 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E71" t="inlineStr">
@@ -3073,7 +4407,30 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E72" t="inlineStr">
@@ -3110,7 +4467,30 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E73" t="inlineStr">
@@ -3147,7 +4527,30 @@
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E74" t="inlineStr">
@@ -3184,7 +4587,30 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
@@ -3221,7 +4647,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/hollow-composite-decking-end-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E76" t="inlineStr">
@@ -3258,7 +4707,30 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-joists-batten</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E77" t="inlineStr">
@@ -3295,7 +4767,30 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/structural-composite-joist</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E78" t="inlineStr">
@@ -3332,7 +4827,30 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-starter-clips-pack-of-50</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E79" t="inlineStr">
@@ -3369,7 +4887,30 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-t-clip-fixings-and-screws</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
@@ -3406,7 +4947,30 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-decking-stainless-clips</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E81" t="inlineStr">
@@ -3443,7 +5007,30 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/m4-40mm-stainless-steel-fibre-cement</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E82" t="inlineStr">
@@ -3480,7 +5067,30 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-heavy-duty-weed-control-mat</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E83" t="inlineStr">
@@ -3517,7 +5127,30 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-weed-mat-pins</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E84" t="inlineStr">
@@ -3554,7 +5187,30 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-composite-decking-cleaner</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
@@ -3591,7 +5247,30 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E86" t="inlineStr">
@@ -3628,7 +5307,30 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/owatrol-compo-care-composite-decking-reviver</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E87" t="inlineStr">
@@ -3702,7 +5404,30 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/universal-sealant-gun-310ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E89" t="inlineStr">
@@ -3739,7 +5464,30 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E90" t="inlineStr">
@@ -3776,7 +5524,30 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E91" t="inlineStr">
@@ -3813,7 +5584,30 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E92" t="inlineStr">
@@ -3850,7 +5644,30 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E93" t="inlineStr">
@@ -3887,7 +5704,30 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E94" t="inlineStr">
@@ -3924,7 +5764,30 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E95" t="inlineStr">
@@ -3961,7 +5824,30 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E96" t="inlineStr">
@@ -3998,7 +5884,30 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
@@ -4035,7 +5944,30 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E98" t="inlineStr">
@@ -4072,7 +6004,30 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E99" t="inlineStr">
@@ -4109,7 +6064,30 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E100" t="inlineStr">
@@ -4146,7 +6124,30 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E101" t="inlineStr">
@@ -4183,7 +6184,30 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
@@ -4220,7 +6244,30 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E103" t="inlineStr">
@@ -4257,7 +6304,30 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
@@ -4294,7 +6364,30 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/woodgrain-wallcladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
@@ -4331,7 +6424,30 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-wall-cladding-starter-strip</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E106" t="inlineStr">
@@ -4368,7 +6484,30 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
@@ -4405,7 +6544,30 @@
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E108" t="inlineStr">
@@ -4442,7 +6604,30 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E109" t="inlineStr">
@@ -4479,7 +6664,30 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-fencing-panel</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E110" t="inlineStr">
@@ -4516,7 +6724,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E111" t="inlineStr">
@@ -4553,7 +6784,30 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
@@ -4590,7 +6844,30 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E113" t="inlineStr">
@@ -4627,7 +6904,30 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-panel-post-3m</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E114" t="inlineStr">
@@ -4664,7 +6964,30 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E115" t="inlineStr">
@@ -4701,7 +7024,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E116" t="inlineStr">
@@ -4738,7 +7084,30 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E117" t="inlineStr">
@@ -4775,7 +7144,30 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/composite-fence-post-caps</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
@@ -4812,7 +7204,30 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E119" t="inlineStr">
@@ -4849,7 +7264,30 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E120" t="inlineStr">
@@ -4886,7 +7324,30 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E121" t="inlineStr">
@@ -4923,7 +7384,30 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E122" t="inlineStr">
@@ -4960,7 +7444,30 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E123" t="inlineStr">
@@ -4997,7 +7504,30 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
@@ -5034,7 +7564,30 @@
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-capstock-pvc-woodgrain-decking-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E125" t="inlineStr">
@@ -5071,7 +7624,30 @@
       </c>
       <c r="D126" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E126" t="inlineStr">
@@ -5108,7 +7684,30 @@
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E127" t="inlineStr">
@@ -5145,7 +7744,30 @@
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E128" t="inlineStr">
@@ -5182,7 +7804,30 @@
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
@@ -5219,7 +7864,30 @@
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E130" t="inlineStr">
@@ -5256,7 +7924,30 @@
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-bullnose</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E131" t="inlineStr">
@@ -5293,7 +7984,30 @@
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E132" t="inlineStr">
@@ -5330,7 +8044,30 @@
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E133" t="inlineStr">
@@ -5367,7 +8104,30 @@
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E134" t="inlineStr">
@@ -5404,7 +8164,30 @@
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
@@ -5441,7 +8224,30 @@
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E136" t="inlineStr">
@@ -5478,7 +8284,30 @@
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-6m-pvc-woodgrain-effect-premium-grade-fascia-board</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E137" t="inlineStr">
@@ -5515,7 +8344,30 @@
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E138" t="inlineStr">
@@ -5552,7 +8404,30 @@
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E139" t="inlineStr">
@@ -5589,7 +8464,30 @@
       </c>
       <c r="D140" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E140" t="inlineStr">
@@ -5626,7 +8524,30 @@
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
@@ -5663,7 +8584,30 @@
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E142" t="inlineStr">
@@ -5700,7 +8644,30 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
@@ -5737,7 +8704,30 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
@@ -5774,7 +8764,30 @@
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E145" t="inlineStr">
@@ -5811,7 +8824,30 @@
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3-66m-fibre-cement-exterior-wall-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E146" t="inlineStr">
@@ -5848,7 +8884,30 @@
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/3m-aluminium-perforated-closure</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
@@ -5885,7 +8944,30 @@
       </c>
       <c r="D148" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E148" t="inlineStr">
@@ -5922,7 +9004,30 @@
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E149" t="inlineStr">
@@ -5959,7 +9064,30 @@
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E150" t="inlineStr">
@@ -5996,7 +9124,30 @@
       </c>
       <c r="D151" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E151" t="inlineStr">
@@ -6033,7 +9184,30 @@
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
@@ -6070,7 +9244,30 @@
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E153" t="inlineStr">
@@ -6107,7 +9304,30 @@
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E154" t="inlineStr">
@@ -6144,7 +9364,30 @@
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-start-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E155" t="inlineStr">
@@ -6181,7 +9424,30 @@
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E156" t="inlineStr">
@@ -6218,7 +9484,30 @@
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
@@ -6255,7 +9544,30 @@
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E158" t="inlineStr">
@@ -6292,7 +9604,30 @@
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E159" t="inlineStr">
@@ -6329,7 +9664,30 @@
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E160" t="inlineStr">
@@ -6366,7 +9724,30 @@
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E161" t="inlineStr">
@@ -6403,7 +9784,30 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
@@ -6440,7 +9844,30 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-symmetric-external-corner-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
@@ -6477,7 +9904,30 @@
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E164" t="inlineStr">
@@ -6514,7 +9964,30 @@
       </c>
       <c r="D165" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E165" t="inlineStr">
@@ -6551,7 +10024,30 @@
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E166" t="inlineStr">
@@ -6588,7 +10084,30 @@
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E167" t="inlineStr">
@@ -6625,7 +10144,30 @@
       </c>
       <c r="D168" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E168" t="inlineStr">
@@ -6662,7 +10204,30 @@
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E169" t="inlineStr">
@@ -6699,7 +10264,30 @@
       </c>
       <c r="D170" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E170" t="inlineStr">
@@ -6736,7 +10324,30 @@
       </c>
       <c r="D171" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-asymmetric-external-window-door</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E171" t="inlineStr">
@@ -6773,7 +10384,30 @@
       </c>
       <c r="D172" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E172" t="inlineStr">
@@ -6810,7 +10444,30 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">
@@ -6847,7 +10504,30 @@
       </c>
       <c r="D174" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E174" t="inlineStr">
@@ -6884,7 +10564,30 @@
       </c>
       <c r="D175" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E175" t="inlineStr">
@@ -6921,7 +10624,30 @@
       </c>
       <c r="D176" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E176" t="inlineStr">
@@ -6958,7 +10684,30 @@
       </c>
       <c r="D177" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E177" t="inlineStr">
@@ -6995,7 +10744,30 @@
       </c>
       <c r="D178" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E178" t="inlineStr">
@@ -7032,7 +10804,30 @@
       </c>
       <c r="D179" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-internal-corner-profile-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E179" t="inlineStr">
@@ -7069,7 +10864,30 @@
       </c>
       <c r="D180" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E180" t="inlineStr">
@@ -7106,7 +10924,30 @@
       </c>
       <c r="D181" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E181" t="inlineStr">
@@ -7143,7 +10984,30 @@
       </c>
       <c r="D182" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E182" t="inlineStr">
@@ -7180,7 +11044,30 @@
       </c>
       <c r="D183" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E183" t="inlineStr">
@@ -7217,7 +11104,30 @@
       </c>
       <c r="D184" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E184" t="inlineStr">
@@ -7254,7 +11164,30 @@
       </c>
       <c r="D185" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E185" t="inlineStr">
@@ -7291,7 +11224,30 @@
       </c>
       <c r="D186" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-double-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E186" t="inlineStr">
@@ -7328,7 +11284,30 @@
       </c>
       <c r="D187" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E187" t="inlineStr">
@@ -7365,7 +11344,30 @@
       </c>
       <c r="D188" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E188" t="inlineStr">
@@ -7402,7 +11404,30 @@
       </c>
       <c r="D189" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E189" t="inlineStr">
@@ -7439,7 +11464,30 @@
       </c>
       <c r="D190" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E190" t="inlineStr">
@@ -7476,7 +11524,30 @@
       </c>
       <c r="D191" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E191" t="inlineStr">
@@ -7513,7 +11584,30 @@
       </c>
       <c r="D192" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E192" t="inlineStr">
@@ -7550,7 +11644,30 @@
       </c>
       <c r="D193" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E193" t="inlineStr">
@@ -7587,7 +11704,30 @@
       </c>
       <c r="D194" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-single-board-connection-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E194" t="inlineStr">
@@ -7624,7 +11764,30 @@
       </c>
       <c r="D195" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E195" t="inlineStr">
@@ -7661,7 +11824,30 @@
       </c>
       <c r="D196" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E196" t="inlineStr">
@@ -7698,7 +11884,30 @@
       </c>
       <c r="D197" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E197" t="inlineStr">
@@ -7735,7 +11944,30 @@
       </c>
       <c r="D198" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E198" t="inlineStr">
@@ -7772,7 +12004,30 @@
       </c>
       <c r="D199" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E199" t="inlineStr">
@@ -7809,7 +12064,30 @@
       </c>
       <c r="D200" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E200" t="inlineStr">
@@ -7846,7 +12124,30 @@
       </c>
       <c r="D201" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-wall-end-trim</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E201" t="inlineStr">
@@ -7883,7 +12184,30 @@
       </c>
       <c r="D202" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E202" t="inlineStr">
@@ -7920,7 +12244,30 @@
       </c>
       <c r="D203" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E203" t="inlineStr">
@@ -7957,7 +12304,30 @@
       </c>
       <c r="D204" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E204" t="inlineStr">
@@ -7994,7 +12364,30 @@
       </c>
       <c r="D205" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E205" t="inlineStr">
@@ -8031,7 +12424,30 @@
       </c>
       <c r="D206" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E206" t="inlineStr">
@@ -8068,7 +12484,30 @@
       </c>
       <c r="D207" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E207" t="inlineStr">
@@ -8105,7 +12544,30 @@
       </c>
       <c r="D208" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E208" t="inlineStr">
@@ -8142,7 +12604,30 @@
       </c>
       <c r="D209" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/fibre-cement-touch-up-paint-500ml</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E209" t="inlineStr">
@@ -8179,7 +12664,30 @@
       </c>
       <c r="D210" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E210" t="inlineStr">
@@ -8216,7 +12724,30 @@
       </c>
       <c r="D211" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E211" t="inlineStr">
@@ -8253,7 +12784,30 @@
       </c>
       <c r="D212" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E212" t="inlineStr">
@@ -8290,7 +12844,30 @@
       </c>
       <c r="D213" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E213" t="inlineStr">
@@ -8327,7 +12904,30 @@
       </c>
       <c r="D214" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E214" t="inlineStr">
@@ -8364,7 +12964,30 @@
       </c>
       <c r="D215" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-handrail-balustrade-system</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E215" t="inlineStr">
@@ -8401,7 +13024,30 @@
       </c>
       <c r="D216" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/aluminium-powder-coated-black-balustrade-handrail-post</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E216" t="inlineStr">
@@ -8438,7 +13084,30 @@
       </c>
       <c r="D217" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/balustrade-handrail-gate-aluminium-powder-coated-material</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E217" t="inlineStr">
@@ -8586,7 +13255,30 @@
       </c>
       <c r="D221" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-cladding-batten-50mm-x-50mm-x-3m-length-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E221" t="inlineStr">
@@ -8623,7 +13315,30 @@
       </c>
       <c r="D222" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-post-100x100</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E222" t="inlineStr">
@@ -8660,7 +13375,30 @@
       </c>
       <c r="D223" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/recycled-plastic-joist-50mm-x-100mm-x-3-6m-length-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E223" t="inlineStr">
@@ -8697,7 +13435,30 @@
       </c>
       <c r="D224" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/cladco-recycled-plastic-joist-50x150-3m-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E224" t="inlineStr">
@@ -8734,7 +13495,30 @@
       </c>
       <c r="D225" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/frame-protection-deck-tape-65mm-x-20m-roll-black</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E225" t="inlineStr">
@@ -8771,7 +13555,30 @@
       </c>
       <c r="D226" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E226" t="inlineStr">
@@ -8808,7 +13615,30 @@
       </c>
       <c r="D227" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E227" t="inlineStr">
@@ -8845,7 +13675,30 @@
       </c>
       <c r="D228" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E228" t="inlineStr">
@@ -8882,7 +13735,30 @@
       </c>
       <c r="D229" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/2m-composite-fencing-steel-rail</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E229" t="inlineStr">
@@ -8919,7 +13795,30 @@
       </c>
       <c r="D230" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E230" t="inlineStr">
@@ -8956,7 +13855,30 @@
       </c>
       <c r="D231" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E231" t="inlineStr">
@@ -8993,7 +13915,30 @@
       </c>
       <c r="D232" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E232" t="inlineStr">
@@ -9030,7 +13975,30 @@
       </c>
       <c r="D233" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E233" t="inlineStr">
@@ -9067,7 +14035,30 @@
       </c>
       <c r="D234" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E234" t="inlineStr">
@@ -9104,7 +14095,30 @@
       </c>
       <c r="D235" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E235" t="inlineStr">
@@ -9141,7 +14155,30 @@
       </c>
       <c r="D236" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E236" t="inlineStr">
@@ -9178,7 +14215,30 @@
       </c>
       <c r="D237" t="inlineStr">
         <is>
-          <t>Error: 403 Client Error: Forbidden for url: https://www.cladco.co.uk/pack-of-100-39mm-blue-c10-stainless-steel-screw-bit-for-fibre-cement-cladding</t>
+          <t xml:space="preserve">Error: Message: no such element: Unable to locate element: {"method":"css selector","selector":"[id="totalprice"]"}
+  (Session info: chrome=142.0.7444.163); For documentation on this error, please visit: https://www.selenium.dev/documentation/webdriver/troubleshooting/errors#nosuchelementexception
+Stacktrace:
+Symbols not available. Dumping unresolved backtrace:
+	0x7ff6677fa235
+	0x7ff667552650
+	0x7ff6672e16dd
+	0x7ff66733a27e
+	0x7ff66733a58c
+	0x7ff66738ed77
+	0x7ff66738baba
+	0x7ff66732b0ed
+	0x7ff66732bf63
+	0x7ff667825d60
+	0x7ff66781fe8a
+	0x7ff667841005
+	0x7ff66756d73e
+	0x7ff667574e3f
+	0x7ff66755b7e4
+	0x7ff66755b99f
+	0x7ff667541908
+	0x7fff71bce8d7
+	0x7fff72a2c53c
+</t>
         </is>
       </c>
       <c r="E237" t="inlineStr">
